--- a/inst/config/repo.xlsx
+++ b/inst/config/repo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45dcb46a42df1333/Projects_COMPLETED_TEMP/2021-2024_FISH4ACP/2026_FISHERIES_STATISTICS_STP/estatisticapesqueiraSTP/inst/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45dcb46a42df1333/Projects_COMPLETED_TEMP/2021-2024_FISH4ACP/2026_FISHERIES_STATISTICS_STP/R/estatisticapesqueiraSTP/inst/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_F25DC773A252ABDACC1048F7895C76B25ADE58F9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06C8D45D-FE10-4943-91DF-2730019114D6}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="11_F25DC773A252ABDACC1048F7895C76B25ADE58F9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB8B453-3EA4-4AB1-B2E5-FD92C2FFB4E1}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="3120" windowWidth="28515" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="285" yWindow="2295" windowWidth="28515" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="repo" sheetId="1" r:id="rId1"/>
@@ -34,34 +34,34 @@
     <t>Dados de pesca de São Tomé e Príncipe</t>
   </si>
   <si>
+    <t>zenodo_instance</t>
+  </si>
+  <si>
+    <t>República Democrática de São Tomé e Príncipe</t>
+  </si>
+  <si>
+    <t>Direção das Pescas e Aquacultura</t>
+  </si>
+  <si>
+    <t>affiliation</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>zenodo_description</t>
+  </si>
+  <si>
+    <t>repository_title</t>
+  </si>
+  <si>
+    <t>zenodo</t>
+  </si>
+  <si>
+    <t>repository_location</t>
+  </si>
+  <si>
     <t>sandbox</t>
-  </si>
-  <si>
-    <t>zenodo_instance</t>
-  </si>
-  <si>
-    <t>República Democrática de São Tomé e Príncipe</t>
-  </si>
-  <si>
-    <t>Direção das Pescas e Aquacultura</t>
-  </si>
-  <si>
-    <t>affiliation</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>zenodo_description</t>
-  </si>
-  <si>
-    <t>repository_title</t>
-  </si>
-  <si>
-    <t>zenodo</t>
-  </si>
-  <si>
-    <t>repository_location</t>
   </si>
 </sst>
 </file>
@@ -400,16 +400,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -417,13 +417,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -454,18 +454,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/inst/config/repo.xlsx
+++ b/inst/config/repo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/45dcb46a42df1333/Projects_COMPLETED_TEMP/2021-2024_FISH4ACP/2026_FISHERIES_STATISTICS_STP/R/estatisticapesqueiraSTP/inst/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_F25DC773A252ABDACC1048F7895C76B25ADE58F9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB8B453-3EA4-4AB1-B2E5-FD92C2FFB4E1}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_F25DC773A252ABDACC1048F7895C76B25ADE58F9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D63F02F3-2775-4301-A342-7C88BF53D5D1}"/>
   <bookViews>
-    <workbookView xWindow="285" yWindow="2295" windowWidth="28515" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="repo" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>ESTATISTICA PESQUEIRA STP</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>repository_location</t>
-  </si>
-  <si>
-    <t>sandbox</t>
   </si>
 </sst>
 </file>
@@ -423,7 +420,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
